--- a/artfynd/A 32997-2026 artfynd.xlsx
+++ b/artfynd/A 32997-2026 artfynd.xlsx
@@ -2508,7 +2508,7 @@
         <v>136319628</v>
       </c>
       <c r="B17" t="n">
-        <v>99641</v>
+        <v>99652</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>136319629</v>
       </c>
       <c r="B18" t="n">
-        <v>110048</v>
+        <v>110059</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 32997-2026 artfynd.xlsx
+++ b/artfynd/A 32997-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136319641</v>
       </c>
       <c r="B2" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>136319686</v>
       </c>
       <c r="B3" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>136319687</v>
       </c>
       <c r="B4" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>136319688</v>
       </c>
       <c r="B5" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>136319689</v>
       </c>
       <c r="B6" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>136319690</v>
       </c>
       <c r="B7" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136319691</v>
       </c>
       <c r="B8" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>136319692</v>
       </c>
       <c r="B9" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>136319694</v>
       </c>
       <c r="B10" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>136319695</v>
       </c>
       <c r="B11" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>136319696</v>
       </c>
       <c r="B12" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>136319697</v>
       </c>
       <c r="B13" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>136319698</v>
       </c>
       <c r="B14" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>136319701</v>
       </c>
       <c r="B15" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>136319645</v>
       </c>
       <c r="B16" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>136319628</v>
       </c>
       <c r="B17" t="n">
-        <v>99652</v>
+        <v>99665</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>136319629</v>
       </c>
       <c r="B18" t="n">
-        <v>110059</v>
+        <v>110072</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 32997-2026 artfynd.xlsx
+++ b/artfynd/A 32997-2026 artfynd.xlsx
@@ -2508,7 +2508,7 @@
         <v>136319628</v>
       </c>
       <c r="B17" t="n">
-        <v>99665</v>
+        <v>99666</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>136319629</v>
       </c>
       <c r="B18" t="n">
-        <v>110072</v>
+        <v>110073</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 32997-2026 artfynd.xlsx
+++ b/artfynd/A 32997-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136319641</v>
       </c>
       <c r="B2" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>136319686</v>
       </c>
       <c r="B3" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>136319687</v>
       </c>
       <c r="B4" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>136319688</v>
       </c>
       <c r="B5" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>136319689</v>
       </c>
       <c r="B6" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>136319690</v>
       </c>
       <c r="B7" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>136319691</v>
       </c>
       <c r="B8" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>136319692</v>
       </c>
       <c r="B9" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>136319694</v>
       </c>
       <c r="B10" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>136319695</v>
       </c>
       <c r="B11" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>136319696</v>
       </c>
       <c r="B12" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>136319697</v>
       </c>
       <c r="B13" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>136319698</v>
       </c>
       <c r="B14" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>136319701</v>
       </c>
       <c r="B15" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>136319645</v>
       </c>
       <c r="B16" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>136319628</v>
       </c>
       <c r="B17" t="n">
-        <v>99666</v>
+        <v>99679</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>136319629</v>
       </c>
       <c r="B18" t="n">
-        <v>110073</v>
+        <v>110086</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 32997-2026 artfynd.xlsx
+++ b/artfynd/A 32997-2026 artfynd.xlsx
@@ -2508,7 +2508,7 @@
         <v>136319628</v>
       </c>
       <c r="B17" t="n">
-        <v>99679</v>
+        <v>99680</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>136319629</v>
       </c>
       <c r="B18" t="n">
-        <v>110086</v>
+        <v>110087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
